--- a/flowboard_database.xlsx
+++ b/flowboard_database.xlsx
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -755,6 +755,126 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PROJ-226</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ai-Detector 2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>gffyttucjhvjhvjyfrt</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PROJ-406</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ai-Detector 3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>knjnhbjvhvfcfyqtugftuqgtugq</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PROJ-179</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ai-Detector 4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mwemj3nrj4htk134hbth234h2g5tgjt</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PROJ-268</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ai-Detector 5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>e,mgkMRKMRGNJRGNERHGWRK</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>0</v>
       </c>
     </row>
